--- a/144/DQ Templates and Instructions/Topic 6 DQ 2/Topic 6 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 6 DQ 2/Topic 6 DQ 2.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 6 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{558D6C02-132F-4F4C-922D-FF511F69F3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F09CFDAD-6075-4C56-B993-2B06F414AD5A}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{558D6C02-132F-4F4C-922D-FF511F69F3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E6015D9-17DA-47BF-A7BB-71A648A0C23D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="7" r:id="rId1"/>
-    <sheet name="Games" sheetId="1" r:id="rId2"/>
-    <sheet name="soln1" sheetId="2" state="hidden" r:id="rId3"/>
-    <sheet name="Random" sheetId="6" state="hidden" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="3" state="hidden" r:id="rId6"/>
+    <sheet name="Users" sheetId="8" state="hidden" r:id="rId2"/>
+    <sheet name="Games" sheetId="1" r:id="rId3"/>
+    <sheet name="soln1" sheetId="2" state="hidden" r:id="rId4"/>
+    <sheet name="Random" sheetId="6" state="hidden" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="5" state="hidden" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="3" state="hidden" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1"/>
   <customWorkbookViews>
     <customWorkbookView name="Richard Ketchersid - Personal View" guid="{13B6492D-170C-45E1-97D8-793CC53D410C}" mergeInterval="0" personalView="1" xWindow="64" yWindow="64" windowWidth="1606" windowHeight="950" tabRatio="500" activeSheetId="1"/>
   </customWorkbookViews>
@@ -84,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="89">
   <si>
     <t>Excel Skills Learned</t>
   </si>
@@ -408,6 +409,15 @@
   <si>
     <t>Ignore the Halo preview you must download and open the file in Excel to correctly see the contents.</t>
   </si>
+  <si>
+    <t>Names</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
+  <si>
+    <t>Pick any 2 out of 35 horses, where the order of selection matters.</t>
+  </si>
 </sst>
 </file>
 
@@ -417,7 +427,7 @@
     <numFmt numFmtId="164" formatCode="0.0000000%"/>
     <numFmt numFmtId="165" formatCode="0.00000%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -535,12 +545,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -832,7 +836,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1014,6 +1018,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1040,6 +1048,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1060,24 +1089,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1494,56 +1505,56 @@
       <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="60"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="60"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="62"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="63"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="60"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="62"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="63"/>
     </row>
     <row r="5" spans="2:9" ht="16.5" thickBot="1">
       <c r="B5" s="38"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="62"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="63"/>
     </row>
     <row r="6" spans="2:9" ht="16.5" thickBot="1">
       <c r="B6" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="63"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="65"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="66"/>
     </row>
     <row r="7" spans="2:9" ht="32.25" thickBot="1">
       <c r="B7" s="39" t="s">
@@ -1554,21 +1565,21 @@
       <c r="B8" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="74"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="69"/>
     </row>
     <row r="9" spans="2:9" ht="16.5" thickBot="1">
       <c r="B9" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="75"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="77"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1584,6 +1595,172 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A91141C-C3D9-4AA2-ABC8-D0BBBA265596}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="57">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <f>Games!C2</f>
+        <v>Your Name Here</v>
+      </c>
+      <c r="F1" s="73" t="str">
+        <f ca="1">IF(M1="ACTIVE", "✓ Tracking Active", "⚠️ ERROR: Enable Iterative Calculations (File &gt; Options &gt; Formulas)")</f>
+        <v>✓ Tracking Active</v>
+      </c>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="1" t="str">
+        <f ca="1">IF(M1="ACTIVE", "ACTIVE", "ACTIVE")</f>
+        <v>ACTIVE</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="str">
+        <f t="shared" ref="A2:A19" ca="1" si="0">IF(D$1&lt;&gt;A3,A3,A2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="str">
+        <f ca="1">IF(D$1&lt;&gt;A21,A21,A20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="str">
+        <f ca="1">IF(C1="","",IF(D$1&lt;&gt;A21,D$1,A21))</f>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="S4+JDzynWP2n+mLldpnV32e3to+jdeyFhU2e2LBF7ZlCPxs+GUlaGRk924zl21J4IWI6tph8MlFYaqDBFzW0Aw==" saltValue="pYIRqrpdnO2DI2H9hvHT5w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="F1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I47"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
@@ -1628,15 +1805,15 @@
     </row>
     <row r="4" spans="1:9" ht="16.5" thickBot="1">
       <c r="A4" s="28"/>
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="67"/>
+      <c r="C4" s="75"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
     </row>
     <row r="5" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="76" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="13" t="s">
@@ -1649,7 +1826,7 @@
       <c r="E5" s="28"/>
     </row>
     <row r="6" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A6" s="69"/>
+      <c r="A6" s="77"/>
       <c r="B6" s="15" t="s">
         <v>15</v>
       </c>
@@ -1661,7 +1838,7 @@
       <c r="F6" s="24"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A7" s="70"/>
+      <c r="A7" s="78"/>
       <c r="B7" s="17" t="s">
         <v>17</v>
       </c>
@@ -1741,12 +1918,10 @@
       <c r="B13" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="31" t="str">
-        <f ca="1">"Pick any 2 out of "&amp;Random!H19&amp;" horses, where the order of selection matters."</f>
-        <v>Pick any 2 out of 35 horses, where the order of selection matters.</v>
+      <c r="C13" s="31" t="s">
+        <v>88</v>
       </c>
       <c r="D13" s="32">
-        <f ca="1">PERMUT(Random!H19,2)</f>
         <v>1190</v>
       </c>
       <c r="E13" s="31" t="s">
@@ -1756,15 +1931,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="27">
-        <f ca="1">F13/D13</f>
+        <f>F13/D13</f>
         <v>8.4033613445378156E-4</v>
       </c>
       <c r="H13" s="26">
-        <f ca="1">(1-G13)/G13</f>
+        <f>(1-G13)/G13</f>
         <v>1189</v>
       </c>
       <c r="I13" s="56" t="str">
-        <f ca="1">"Your odds of winning are 1 to "&amp;H13&amp;"!"</f>
+        <f>"Your odds of winning are 1 to "&amp;H13&amp;"!"</f>
         <v>Your odds of winning are 1 to 1189!</v>
       </c>
     </row>
@@ -1962,7 +2137,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="HpSVuIj+zgNW+OGH+y3EYJh1IVNJ6pDuptQopRAB2kkAwyWtrd84kirLSmsDdZUhXiZ24VuP6xT1gsoVeoiR3w==" saltValue="C3QcD4O3BRIVjpYoQjrc6g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="D4BTk7rpf94S4H2GN6Se0pFx6PDrg0BpRq1aaH5PbKv+I25zFFdBQ4CHL2poeIuS93NT/OBaOt7LegEZuqZMVg==" saltValue="eowzrkvLKBk6WLY98KMJJw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <customSheetViews>
     <customSheetView guid="{13B6492D-170C-45E1-97D8-793CC53D410C}" showRuler="0" topLeftCell="B1">
       <selection activeCell="C3" sqref="C3"/>
@@ -2031,7 +2206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1D97F0-2451-47BE-A51B-12A3F1003A2C}">
   <dimension ref="A1:I47"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
@@ -2076,15 +2251,15 @@
     </row>
     <row r="4" spans="1:9" ht="16.5" thickBot="1">
       <c r="A4" s="28"/>
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="67"/>
+      <c r="C4" s="75"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
     </row>
     <row r="5" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="76" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="13" t="s">
@@ -2097,7 +2272,7 @@
       <c r="E5" s="28"/>
     </row>
     <row r="6" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A6" s="69"/>
+      <c r="A6" s="77"/>
       <c r="B6" s="15" t="s">
         <v>15</v>
       </c>
@@ -2109,7 +2284,7 @@
       <c r="F6" s="24"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A7" s="70"/>
+      <c r="A7" s="78"/>
       <c r="B7" s="17" t="s">
         <v>17</v>
       </c>
@@ -2511,7 +2686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70EFFDD7-AE6B-4532-BBBB-506CEF972D40}">
   <dimension ref="A1:W55"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -4543,7 +4718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AEDF658-1B33-4733-9197-78E9FD0425A9}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -4707,61 +4882,61 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B00329-900E-4C44-ABF7-150FAC5BFA0C}">
   <dimension ref="C4:G10"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData>
     <row r="4" spans="3:7">
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
     </row>
     <row r="5" spans="3:7">
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
     </row>
     <row r="6" spans="3:7">
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
     </row>
     <row r="7" spans="3:7">
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
     </row>
     <row r="8" spans="3:7">
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="79"/>
     </row>
     <row r="9" spans="3:7">
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="79"/>
+      <c r="G9" s="79"/>
     </row>
     <row r="10" spans="3:7">
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -4780,16 +4955,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -5006,6 +5171,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5016,16 +5191,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF39485D-C01E-4ECC-A97D-DD7E1E83D4C0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90817591-2806-4B51-9D1C-6BC766992EA6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5044,6 +5209,16 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF39485D-C01E-4ECC-A97D-DD7E1E83D4C0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE888125-757F-4287-A413-B81F0A459F37}">
   <ds:schemaRefs>
